--- a/Ondrelle-Vacation-Requests.xlsx
+++ b/Ondrelle-Vacation-Requests.xlsx
@@ -1,69 +1,121 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cyclotron-my.sharepoint.com/personal/mohamed_derhalli_cyclotron_com/Documents/Clients/Revlon/Ondrelle/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_8173B3984EECA1B0D28A37769FC78751B67187A9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF01684F-026C-48F3-8557-8B805EC9C304}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vacation Requests" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Vacation Requests" sheetId="1" r:id="rId1"/>
+    <sheet name="Read Me" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>From Date</t>
+  </si>
+  <si>
+    <t>End Date</t>
+  </si>
+  <si>
+    <t>Justification</t>
+  </si>
+  <si>
+    <t>Ondrelle Vacation Requests — starter workbook</t>
+  </si>
+  <si>
+    <t>Used in Lab 1.5 to create the Vacation Requests SharePoint list (New &gt; List &gt; From Excel).</t>
+  </si>
+  <si>
+    <t>SharePoint imports only the formatted table on the 'Vacation Requests' sheet. This sheet is ignored.</t>
+  </si>
+  <si>
+    <t>Columns</t>
+  </si>
+  <si>
+    <t>Title — a short name for the request (text).</t>
+  </si>
+  <si>
+    <t>From Date — first day of vacation (set to Date and Time during import).</t>
+  </si>
+  <si>
+    <t>End Date — last day of vacation (set to Date and Time during import).</t>
+  </si>
+  <si>
+    <t>Justification — the reason for the request (text; Multiple lines of text works well).</t>
+  </si>
+  <si>
+    <t>The three rows in the table are sample data. They become list items when imported; delete them in SharePoint if you want an empty list.</t>
+  </si>
+  <si>
+    <t>Ondrelle is a fictional company created for this workshop. All data is for training purposes only.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="7">
-    <font>
+  <fonts count="7" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="Arial"/>
-      <b val="1"/>
+    </font>
+    <font>
       <sz val="11"/>
-    </font>
-    <font>
       <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF1F3864"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="11"/>
-    </font>
-    <font>
+      <color rgb="FF333333"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001F3864"/>
-      <sz val="14"/>
-    </font>
-    <font>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
       <name val="Arial"/>
-      <color rgb="00333333"/>
-      <sz val="11"/>
-    </font>
-    <font>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF333333"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00333333"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00333333"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -82,112 +134,53 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="VacationRequests" displayName="VacationRequests" ref="A1:D4" headerRowCount="1">
-  <autoFilter ref="A1:D4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="VacationRequests" displayName="VacationRequests" ref="A1:D4">
+  <autoFilter ref="A1:D4" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" name="Title"/>
-    <tableColumn id="2" name="From Date"/>
-    <tableColumn id="3" name="End Date"/>
-    <tableColumn id="4" name="Justification"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Title"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="From Date"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="End Date"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Justification"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -475,199 +468,132 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>From Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>End Date</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Justification</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Summer family vacation</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="n">
-        <v>46377</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>46387</v>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>Annual family holiday travel over the winter break.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Wedding attendance</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n">
-        <v>46430</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>46433</v>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Attending a family member's wedding out of town.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Personal rest days</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>46454</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>46456</v>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Taking accrued vacation days to rest after a project launch.</t>
-        </is>
-      </c>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="3"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="5"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="3"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="5"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="3"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col min="1" max="1" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>Ondrelle Vacation Requests — starter workbook</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="7" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>Used in Lab 1.5 to create the Vacation Requests SharePoint list (New &gt; List &gt; From Excel).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>SharePoint imports only the formatted table on the 'Vacation Requests' sheet. This sheet is ignored.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Columns</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Title — a short name for the request (text).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>From Date — first day of vacation (set to Date and Time during import).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>End Date — last day of vacation (set to Date and Time during import).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Justification — the reason for the request (text; Multiple lines of text works well).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>The three rows in the table are sample data. They become list items when imported; delete them in SharePoint if you want an empty list.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>Ondrelle is a fictional company created for this workshop. All data is for training purposes only.</t>
-        </is>
+    <row r="1" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7"/>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7"/>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7"/>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7"/>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{2f6acb07-0c76-4b4a-9d9f-12088a7c315d}" enabled="1" method="Privileged" siteId="{6583636b-d156-492e-86ce-b8fccb790df1}" removed="0"/>
+</clbl:labelList>
 </file>
--- a/Ondrelle-Vacation-Requests.xlsx
+++ b/Ondrelle-Vacation-Requests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cyclotron-my.sharepoint.com/personal/mohamed_derhalli_cyclotron_com/Documents/Clients/Revlon/Ondrelle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_8173B3984EECA1B0D28A37769FC78751B67187A9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF01684F-026C-48F3-8557-8B805EC9C304}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_8173B3984EECA1B0D28A37769FC78751B67187A9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC9E3986-265B-4B46-8812-39CB4097E340}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -172,8 +172,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="VacationRequests" displayName="VacationRequests" ref="A1:D4">
-  <autoFilter ref="A1:D4" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="VacationRequests" displayName="VacationRequests" ref="A1:D2" insertRow="1">
+  <autoFilter ref="A1:D2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Title"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="From Date"/>
@@ -469,7 +469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -496,18 +496,6 @@
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="5"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="3"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
